--- a/Data/g13.3b.xlsx
+++ b/Data/g13.3b.xlsx
@@ -453,16 +453,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,16 +473,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,11 +498,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -518,11 +518,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -533,16 +533,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -553,16 +553,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -578,15 +578,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.18</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11º</t>
+          <t>16º</t>
         </is>
       </c>
     </row>
@@ -598,11 +598,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.13</v>
+        <v>0.38</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
@@ -614,11 +614,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.2</v>
+        <v>0.63</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
